--- a/public/Шаблон загрузки.xlsx
+++ b/public/Шаблон загрузки.xlsx
@@ -610,7 +610,7 @@
         <v>ai сервис, нейросеть, генерация текста, ассистент для кода, английское название, синонимы</v>
       </c>
       <c r="J3">
-        <v>779</v>
+        <v>100</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -618,8 +618,8 @@
       <c r="L3" t="str">
         <v>USD</v>
       </c>
-      <c r="M3">
-        <v>1.85</v>
+      <c r="M3" t="str">
+        <v/>
       </c>
       <c r="N3">
         <v>0</v>
@@ -690,13 +690,13 @@
         <v/>
       </c>
       <c r="K4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L4" t="str">
         <v>EUR</v>
       </c>
-      <c r="M4">
-        <v>1.85</v>
+      <c r="M4" t="str">
+        <v/>
       </c>
       <c r="N4">
         <v>0</v>
@@ -812,7 +812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve">  рублёвая цена = себестоимость × курс ЦБ РФ на дату загрузки × коэффициент наценки (markup_coeff, база 1.85).</v>
+        <v xml:space="preserve">  рублёвая цена = себестоимость × курс ЦБ РФ на дату загрузки × коэффициент наценки (markup_coeff).</v>
       </c>
     </row>
     <row r="14">
@@ -822,7 +822,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>• markup_coeff — индивидуальный коэффициент наценки товара. Пусто = база 1.85.</v>
+        <v>• markup_coeff — индивидуальный коэффициент наценки товара. Пусто = базовый коэффициент из настроек.</v>
       </c>
     </row>
     <row r="16">
